--- a/SGC-CKN/Excel/ac7a222b-dba8-4954-b3c5-1b32b8b71503_Lô_CT-02_P2-57_D800_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/ac7a222b-dba8-4954-b3c5-1b32b8b71503_Lô_CT-02_P2-57_D800_08-04-2026.xlsx
@@ -1145,7 +1145,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.69</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.24</v>
@@ -1154,10 +1154,10 @@
         <v>0.27</v>
       </c>
       <c r="I11" s="5">
-        <v>0.55</v>
+        <v>1.24</v>
       </c>
       <c r="J11" s="8">
-        <v>2.06</v>
+        <v>4.65</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1218,16 +1218,16 @@
         <v>-4.34</v>
       </c>
       <c r="G13" s="13">
-        <v>-7.69</v>
+        <v>-7.64</v>
       </c>
       <c r="H13" s="13">
         <v>0.48</v>
       </c>
       <c r="I13" s="13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="12">
-        <v>6.93</v>
+        <v>6.83</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1250,7 +1250,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="16">
-        <v>-7.69</v>
+        <v>-7.64</v>
       </c>
       <c r="G14" s="16">
         <v>-16.44</v>
@@ -1259,10 +1259,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" s="16">
-        <v>8.75</v>
+        <v>8.8</v>
       </c>
       <c r="J14" s="12">
-        <v>9.38</v>
+        <v>9.43</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1323,16 +1323,16 @@
         <v>-21.64</v>
       </c>
       <c r="G16" s="22">
-        <v>-25.14</v>
+        <v>-25.64</v>
       </c>
       <c r="H16" s="22">
         <v>0.57</v>
       </c>
       <c r="I16" s="22">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="12">
-        <v>6.18</v>
+        <v>7.06</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1355,7 +1355,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-25.14</v>
+        <v>-25.64</v>
       </c>
       <c r="G17" s="25">
         <v>-39.1</v>
@@ -1364,10 +1364,10 @@
         <v>2.17</v>
       </c>
       <c r="I17" s="25">
-        <v>13.96</v>
+        <v>13.46</v>
       </c>
       <c r="J17" s="12">
-        <v>6.44</v>
+        <v>6.21</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.69</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.24</v>
@@ -1566,10 +1566,10 @@
         <v>0.27</v>
       </c>
       <c r="H2" s="5">
-        <v>0.55</v>
+        <v>1.24</v>
       </c>
       <c r="I2" s="8">
-        <v>2.06</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1618,16 +1618,16 @@
         <v>-4.34</v>
       </c>
       <c r="F4" s="13">
-        <v>-7.69</v>
+        <v>-7.64</v>
       </c>
       <c r="G4" s="13">
         <v>0.48</v>
       </c>
       <c r="H4" s="13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="12">
-        <v>6.93</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-7.69</v>
+        <v>-7.64</v>
       </c>
       <c r="F5" s="16">
         <v>-16.44</v>
@@ -1653,10 +1653,10 @@
         <v>0.93</v>
       </c>
       <c r="H5" s="16">
-        <v>8.75</v>
+        <v>8.8</v>
       </c>
       <c r="I5" s="12">
-        <v>9.38</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1705,16 +1705,16 @@
         <v>-21.64</v>
       </c>
       <c r="F7" s="22">
-        <v>-25.14</v>
+        <v>-25.64</v>
       </c>
       <c r="G7" s="22">
         <v>0.57</v>
       </c>
       <c r="H7" s="22">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="12">
-        <v>6.18</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-25.14</v>
+        <v>-25.64</v>
       </c>
       <c r="F8" s="25">
         <v>-39.1</v>
@@ -1740,10 +1740,10 @@
         <v>2.17</v>
       </c>
       <c r="H8" s="25">
-        <v>13.96</v>
+        <v>13.46</v>
       </c>
       <c r="I8" s="12">
-        <v>6.44</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.69</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.45</v>
@@ -1798,10 +1798,10 @@
         <v>7.8</v>
       </c>
       <c r="H10" s="33">
-        <v>43.76</v>
+        <v>44.45</v>
       </c>
       <c r="I10" s="33">
-        <v>5.61</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
